--- a/sc0_urls.xlsx
+++ b/sc0_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
   <si>
     <t>x</t>
   </si>
@@ -533,6 +533,30 @@
     <t>172</t>
   </si>
   <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2c1a3b4f/Heart-of-Midlothian-Rangers-August-3-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -581,45 +605,45 @@
     <t>https://fbref.com/en/matches/9dc2d830/St-Mirren-Celtic-August-25-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a0f450ae/Motherwell-Heart-of-Midlothian-August-25-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7df69c15/Aberdeen-Kilmarnock-August-25-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a0f450ae/Motherwell-Heart-of-Midlothian-August-25-2024-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/8254a65d/St-Johnstone-Motherwell-August-31-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/30131e2c/Dundee-St-Mirren-August-31-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8254a65d/St-Johnstone-Motherwell-August-31-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/b15c46f2/Ross-County-Aberdeen-August-31-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/20a083c1/Old-Firm-Derby-Celtic-Rangers-September-1-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f669adee/Kilmarnock-Hibernian-September-1-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5e8392ec/Heart-of-Midlothian-Dundee-United-September-1-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f669adee/Kilmarnock-Hibernian-September-1-2024-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/4d21a7b4/Ross-County-Dundee-September-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/428dec43/Aberdeen-Motherwell-September-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/56bfe1e9/Hibernian-St-Johnstone-September-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8f673980/Celtic-Heart-of-Midlothian-September-14-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/15ed5511/St-Mirren-Kilmarnock-September-14-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/428dec43/Aberdeen-Motherwell-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/4d21a7b4/Ross-County-Dundee-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/56bfe1e9/Hibernian-St-Johnstone-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8f673980/Celtic-Heart-of-Midlothian-September-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/77c13f3b/Dundee-United-Rangers-September-15-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -629,33 +653,33 @@
     <t>https://fbref.com/en/matches/eca23e74/St-Mirren-Heart-of-Midlothian-September-21-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d3bc079b/Kilmarnock-Dundee-United-September-28-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/9efd8a62/Heart-of-Midlothian-Ross-County-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d3bc079b/Kilmarnock-Dundee-United-September-28-2024-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/ed92dd8c/Dundee-Aberdeen-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d7b2ed59/Motherwell-St-Mirren-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ed92dd8c/Dundee-Aberdeen-September-28-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a30220aa/St-Johnstone-Celtic-September-28-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/fdb926ed/Rangers-Hibernian-September-29-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b6b34b08/Dundee-Kilmarnock-October-5-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1bd44a80/St-Mirren-Dundee-United-October-5-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/91abdab9/Hibernian-Motherwell-October-5-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b6b34b08/Dundee-Kilmarnock-October-5-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/519d3fb9/Ross-County-Celtic-October-6-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -665,30 +689,30 @@
     <t>https://fbref.com/en/matches/1b839ace/Rangers-St-Johnstone-October-6-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3bd671ec/St-Johnstone-Ross-County-October-19-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3c3fa65d/Heart-of-Midlothian-St-Mirren-October-19-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b89ef4e2/Celtic-Aberdeen-October-19-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/168d4a08/Motherwell-Dundee-October-19-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3bd671ec/St-Johnstone-Ross-County-October-19-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3c3fa65d/Heart-of-Midlothian-St-Mirren-October-19-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b89ef4e2/Celtic-Aberdeen-October-19-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d4e66239/Dundee-United-Hibernian-October-19-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/62a8b15b/Kilmarnock-Rangers-October-20-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d1729397/Ross-County-Kilmarnock-October-26-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/18f3e515/Dundee-St-Johnstone-October-26-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d1729397/Ross-County-Kilmarnock-October-26-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/41db5901/Aberdeen-Dundee-United-October-26-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -701,21 +725,21 @@
     <t>https://fbref.com/en/matches/a3103c61/Motherwell-Celtic-October-27-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b8e6969e/St-Mirren-St-Johnstone-October-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/243c9ff0/Heart-of-Midlothian-Kilmarnock-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fb394c66/Dundee-United-Motherwell-October-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5e06d4fa/Celtic-Dundee-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9066db1d/Ross-County-Hibernian-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b8e6969e/St-Mirren-St-Johnstone-October-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fb394c66/Dundee-United-Motherwell-October-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2bc330fa/Aberdeen-Rangers-October-30-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -731,15 +755,15 @@
     <t>https://fbref.com/en/matches/c1b32f12/Dundee-Kilmarnock-November-3-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8fb2341b/Hibernian-St-Mirren-November-9-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/37bdcada/Dundee-United-Ross-County-November-9-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0ca6d764/Motherwell-St-Johnstone-November-9-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/37bdcada/Dundee-United-Ross-County-November-9-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8fb2341b/Hibernian-St-Mirren-November-9-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fddc2b46/Aberdeen-Dundee-November-9-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -749,12 +773,12 @@
     <t>https://fbref.com/en/matches/ea1763a1/Rangers-Heart-of-Midlothian-November-10-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4c5a8bca/Ross-County-Motherwell-November-23-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2599fc31/St-Johnstone-Kilmarnock-November-23-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4c5a8bca/Ross-County-Motherwell-November-23-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1aaa7ff5/Rangers-Dundee-United-November-23-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -770,18 +794,18 @@
     <t>https://fbref.com/en/matches/7b93868a/Hibernian-Aberdeen-November-26-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4c74869f/Celtic-Ross-County-November-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/984b304b/Motherwell-Hibernian-November-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e61740ec/Dundee-United-St-Mirren-November-30-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2316c31e/Kilmarnock-Dundee-November-30-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4c74869f/Celtic-Ross-County-November-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/984b304b/Motherwell-Hibernian-November-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e61740ec/Dundee-United-St-Mirren-November-30-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/32ef90a0/St-Johnstone-Rangers-December-1-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -800,27 +824,27 @@
     <t>https://fbref.com/en/matches/32dd944a/Heart-of-Midlothian-Dundee-December-7-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bc87d012/St-Mirren-Motherwell-December-7-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/da6ed2c3/Celtic-Hibernian-December-7-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d042afb3/Aberdeen-St-Johnstone-December-7-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/912d8208/Dundee-United-Kilmarnock-December-7-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bc87d012/St-Mirren-Motherwell-December-7-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d042afb3/Aberdeen-St-Johnstone-December-7-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/da6ed2c3/Celtic-Hibernian-December-7-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/33bc939b/Ross-County-Rangers-December-8-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7c8f9957/Hibernian-Ross-County-December-14-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1ebb323f/St-Johnstone-St-Mirren-December-14-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7c8f9957/Hibernian-Ross-County-December-14-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/94d0e535/Motherwell-Dundee-United-December-14-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -851,15 +875,15 @@
     <t>https://fbref.com/en/matches/2d98e4f1/St-Johnstone-Dundee-United-December-26-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3d045017/Celtic-Motherwell-December-26-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa3d2759/Dundee-Ross-County-December-26-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/377cdd1e/Kilmarnock-Aberdeen-December-26-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3d045017/Celtic-Motherwell-December-26-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fa3d2759/Dundee-Ross-County-December-26-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e532f712/St-Mirren-Rangers-December-26-2024-Scottish-Premiership</t>
   </si>
   <si>
@@ -869,33 +893,33 @@
     <t>https://fbref.com/en/matches/7c89743b/St-Mirren-Dundee-December-29-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9d62990c/Hibernian-Kilmarnock-December-29-2024-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/88614304/Motherwell-Rangers-December-29-2024-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7e37ddf0/Ross-County-Heart-of-Midlothian-December-29-2024-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/88614304/Motherwell-Rangers-December-29-2024-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9d62990c/Hibernian-Kilmarnock-December-29-2024-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e83b0ccb/Dundee-United-Aberdeen-December-29-2024-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e9c07aa0/Kilmarnock-St-Mirren-January-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/05f4ed4c/Old-Firm-Derby-Rangers-Celtic-January-2-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cea70176/Aberdeen-Ross-County-January-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/940ef160/Heart-of-Midlothian-Motherwell-January-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/840ef9c9/St-Johnstone-Hibernian-January-2-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/940ef160/Heart-of-Midlothian-Motherwell-January-2-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cea70176/Aberdeen-Ross-County-January-2-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e9c07aa0/Kilmarnock-St-Mirren-January-2-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/372f087d/Dundee-Dundee-United-January-2-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -905,6 +929,9 @@
     <t>https://fbref.com/en/matches/e6e0081b/Motherwell-Aberdeen-January-5-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/edbffc0c/Kilmarnock-Ross-County-January-5-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1c66a7c9/Celtic-St-Mirren-January-5-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -914,15 +941,12 @@
     <t>https://fbref.com/en/matches/9b7e92cb/St-Johnstone-Dundee-January-5-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/edbffc0c/Kilmarnock-Ross-County-January-5-2025-Scottish-Premiership</t>
+    <t>https://fbref.com/en/matches/3da36d25/Celtic-Dundee-United-January-8-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/308f66e0/Kilmarnock-Motherwell-January-8-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3da36d25/Celtic-Dundee-United-January-8-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9b632d5a/Dundee-Rangers-January-9-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -935,42 +959,42 @@
     <t>https://fbref.com/en/matches/e2a8d725/Hibernian-Motherwell-January-11-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a02065d3/Rangers-St-Johnstone-January-12-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/78f14c19/Aberdeen-Heart-of-Midlothian-January-12-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a02065d3/Rangers-St-Johnstone-January-12-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/615ed3c7/Dundee-Celtic-January-14-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/ac81a486/Rangers-Aberdeen-January-15-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d79cd451/Aberdeen-St-Mirren-January-25-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e531ac9a/Heart-of-Midlothian-Kilmarnock-January-25-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/90014a11/St-Johnstone-Motherwell-January-25-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3637272e/Ross-County-Hibernian-January-25-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/90014a11/St-Johnstone-Motherwell-January-25-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d79cd451/Aberdeen-St-Mirren-January-25-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e531ac9a/Heart-of-Midlothian-Kilmarnock-January-25-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/30670ab2/Dundee-United-Rangers-January-26-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3ad7bc5e/Hibernian-Aberdeen-February-1-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0757dc49/St-Mirren-St-Johnstone-February-1-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/300f7d2e/Dundee-Heart-of-Midlothian-February-1-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3ad7bc5e/Hibernian-Aberdeen-February-1-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8cd0becf/Kilmarnock-Dundee-United-February-1-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -983,18 +1007,18 @@
     <t>https://fbref.com/en/matches/66f78d4e/Celtic-Dundee-February-5-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d5d17424/Kilmarnock-St-Johnstone-February-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6ec02fb0/Dundee-Aberdeen-February-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d0ae9d90/Motherwell-Ross-County-February-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6a1f684d/Celtic-Dundee-United-February-15-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6ec02fb0/Dundee-Aberdeen-February-15-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d0ae9d90/Motherwell-Ross-County-February-15-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d5d17424/Kilmarnock-St-Johnstone-February-15-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ec8d1ecf/Heart-of-Midlothian-Rangers-February-16-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1004,18 +1028,18 @@
     <t>https://fbref.com/en/matches/0b62e5ac/Hibernian-Celtic-February-22-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ea261585/Aberdeen-Kilmarnock-February-22-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cb800241/Dundee-United-Motherwell-February-22-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3755a2f2/Rangers-St-Mirren-February-22-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a4110188/Ross-County-Dundee-February-22-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cb800241/Dundee-United-Motherwell-February-22-2025-Scottish-Premiership</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ea261585/Aberdeen-Kilmarnock-February-22-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/baa42a3b/St-Johnstone-Heart-of-Midlothian-February-23-2025-Scottish-Premiership</t>
   </si>
   <si>
@@ -1037,16 +1061,40 @@
     <t>https://fbref.com/en/matches/1e557ac5/Kilmarnock-Rangers-February-26-2025-Scottish-Premiership</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/bd56f1be/Dundee-St-Johnstone-March-1-2025-Scottish-Premiership</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/50f69ff9/Rangers-Motherwell-March-1-2025-Scottish-Premiership</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/bd56f1be/Dundee-St-Johnstone-March-1-2025-Scottish-Premiership</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ea15fb4e/Ross-County-Kilmarnock-March-1-2025-Scottish-Premiership</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5dd5b07f/St-Mirren-Celtic-March-1-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1d333832/Hibernian-Heart-of-Midlothian-March-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/995a849b/Aberdeen-Dundee-United-March-2-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a427092f/Heart-of-Midlothian-Ross-County-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3316909/Kilmarnock-Hibernian-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/908b7821/St-Johnstone-Aberdeen-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8615de15/Motherwell-St-Mirren-March-15-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9457d08f/Old-Firm-Derby-Celtic-Rangers-March-16-2025-Scottish-Premiership</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2a374a4/Dundee-United-Dundee-March-16-2025-Scottish-Premiership</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3">
@@ -1113,7 +1161,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4">
@@ -1121,7 +1169,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
@@ -1129,7 +1177,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
@@ -1137,7 +1185,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
@@ -1145,7 +1193,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -1153,7 +1201,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
@@ -1161,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -1169,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -1177,7 +1225,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -1185,7 +1233,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -1193,7 +1241,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14">
@@ -1201,7 +1249,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15">
@@ -1209,7 +1257,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
@@ -1217,7 +1265,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
@@ -1225,7 +1273,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
@@ -1233,7 +1281,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
@@ -1241,7 +1289,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1297,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
@@ -1257,7 +1305,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
@@ -1265,7 +1313,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23">
@@ -1273,7 +1321,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24">
@@ -1281,7 +1329,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25">
@@ -1289,7 +1337,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26">
@@ -1297,7 +1345,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
@@ -1305,7 +1353,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28">
@@ -1313,7 +1361,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29">
@@ -1321,7 +1369,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30">
@@ -1329,7 +1377,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31">
@@ -1337,7 +1385,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32">
@@ -1345,7 +1393,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33">
@@ -1353,7 +1401,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34">
@@ -1361,7 +1409,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35">
@@ -1369,7 +1417,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -1377,7 +1425,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37">
@@ -1385,7 +1433,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38">
@@ -1393,7 +1441,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39">
@@ -1401,7 +1449,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40">
@@ -1409,7 +1457,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41">
@@ -1417,7 +1465,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42">
@@ -1425,7 +1473,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43">
@@ -1433,7 +1481,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44">
@@ -1441,7 +1489,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45">
@@ -1449,7 +1497,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46">
@@ -1457,7 +1505,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47">
@@ -1465,7 +1513,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48">
@@ -1473,7 +1521,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49">
@@ -1481,7 +1529,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50">
@@ -1489,7 +1537,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51">
@@ -1497,7 +1545,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52">
@@ -1505,7 +1553,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53">
@@ -1513,7 +1561,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54">
@@ -1521,7 +1569,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55">
@@ -1529,7 +1577,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56">
@@ -1537,7 +1585,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57">
@@ -1545,7 +1593,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58">
@@ -1553,7 +1601,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59">
@@ -1561,7 +1609,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60">
@@ -1569,7 +1617,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61">
@@ -1577,7 +1625,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62">
@@ -1585,7 +1633,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63">
@@ -1593,7 +1641,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64">
@@ -1601,7 +1649,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65">
@@ -1609,7 +1657,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66">
@@ -1617,7 +1665,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67">
@@ -1625,7 +1673,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="68">
@@ -1633,7 +1681,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="69">
@@ -1641,7 +1689,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70">
@@ -1649,7 +1697,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71">
@@ -1657,7 +1705,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72">
@@ -1665,7 +1713,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73">
@@ -1673,7 +1721,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74">
@@ -1681,7 +1729,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75">
@@ -1689,7 +1737,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76">
@@ -1697,7 +1745,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77">
@@ -1705,7 +1753,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78">
@@ -1713,7 +1761,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79">
@@ -1721,7 +1769,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80">
@@ -1729,7 +1777,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81">
@@ -1737,7 +1785,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82">
@@ -1745,7 +1793,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83">
@@ -1753,7 +1801,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="84">
@@ -1761,7 +1809,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85">
@@ -1769,7 +1817,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86">
@@ -1777,7 +1825,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87">
@@ -1785,7 +1833,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88">
@@ -1793,7 +1841,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89">
@@ -1801,7 +1849,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90">
@@ -1809,7 +1857,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91">
@@ -1817,7 +1865,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92">
@@ -1825,7 +1873,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="93">
@@ -1833,7 +1881,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94">
@@ -1841,7 +1889,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95">
@@ -1849,7 +1897,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96">
@@ -1857,7 +1905,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97">
@@ -1865,7 +1913,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98">
@@ -1873,7 +1921,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99">
@@ -1881,7 +1929,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="100">
@@ -1889,7 +1937,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="101">
@@ -1897,7 +1945,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="102">
@@ -1905,7 +1953,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="103">
@@ -1913,7 +1961,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="104">
@@ -1921,7 +1969,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105">
@@ -1929,7 +1977,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="106">
@@ -1937,7 +1985,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107">
@@ -1945,7 +1993,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108">
@@ -1953,7 +2001,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="109">
@@ -1961,7 +2009,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110">
@@ -1969,7 +2017,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="111">
@@ -1977,7 +2025,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="112">
@@ -1985,7 +2033,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113">
@@ -1993,7 +2041,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="114">
@@ -2001,7 +2049,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115">
@@ -2009,7 +2057,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="116">
@@ -2017,7 +2065,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117">
@@ -2025,7 +2073,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="118">
@@ -2033,7 +2081,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="119">
@@ -2041,7 +2089,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="120">
@@ -2049,7 +2097,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="121">
@@ -2057,7 +2105,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122">
@@ -2065,7 +2113,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="123">
@@ -2073,7 +2121,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="124">
@@ -2081,7 +2129,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125">
@@ -2089,7 +2137,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126">
@@ -2097,7 +2145,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="127">
@@ -2105,7 +2153,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
@@ -2113,7 +2161,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129">
@@ -2121,7 +2169,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130">
@@ -2129,7 +2177,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="131">
@@ -2137,7 +2185,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="132">
@@ -2145,7 +2193,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="133">
@@ -2153,7 +2201,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="134">
@@ -2161,7 +2209,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="135">
@@ -2169,7 +2217,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="136">
@@ -2177,7 +2225,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="137">
@@ -2185,7 +2233,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="138">
@@ -2193,7 +2241,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="139">
@@ -2201,7 +2249,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="140">
@@ -2209,7 +2257,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141">
@@ -2217,7 +2265,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="142">
@@ -2225,7 +2273,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="143">
@@ -2233,7 +2281,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="144">
@@ -2241,7 +2289,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="145">
@@ -2249,7 +2297,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146">
@@ -2257,7 +2305,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="147">
@@ -2265,7 +2313,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="148">
@@ -2273,7 +2321,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="149">
@@ -2281,7 +2329,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="150">
@@ -2289,7 +2337,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="151">
@@ -2297,7 +2345,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="152">
@@ -2305,7 +2353,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="153">
@@ -2313,7 +2361,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="154">
@@ -2321,7 +2369,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="155">
@@ -2329,7 +2377,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="156">
@@ -2337,7 +2385,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="157">
@@ -2345,7 +2393,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="158">
@@ -2353,7 +2401,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="159">
@@ -2361,7 +2409,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="160">
@@ -2369,7 +2417,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="161">
@@ -2377,7 +2425,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="162">
@@ -2385,7 +2433,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="163">
@@ -2393,7 +2441,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="164">
@@ -2401,7 +2449,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="165">
@@ -2409,7 +2457,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="166">
@@ -2417,7 +2465,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="167">
@@ -2425,7 +2473,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="168">
@@ -2433,7 +2481,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="169">
@@ -2441,7 +2489,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="170">
@@ -2449,7 +2497,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="171">
@@ -2457,7 +2505,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="172">
@@ -2465,7 +2513,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173">
@@ -2473,7 +2521,71 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>344</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
